--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31120" windowHeight="13760"/>
+    <workbookView windowWidth="31120" windowHeight="13700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="909">
   <si>
     <t>日期</t>
   </si>
@@ -3721,7 +3721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z887"/>
+  <dimension ref="A1:Z888"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -74688,6 +74688,86 @@
         <v>550.46</v>
       </c>
     </row>
+    <row r="888" spans="1:26">
+      <c r="A888" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B888" t="s">
+        <v>27</v>
+      </c>
+      <c r="C888" s="1">
+        <v>541.06</v>
+      </c>
+      <c r="D888" s="1">
+        <v>519.82</v>
+      </c>
+      <c r="E888" s="1">
+        <v>492.99</v>
+      </c>
+      <c r="F888" s="1">
+        <v>479.24</v>
+      </c>
+      <c r="G888" s="1">
+        <v>434.52</v>
+      </c>
+      <c r="H888" s="1">
+        <v>419.65</v>
+      </c>
+      <c r="I888" s="1">
+        <v>422.64</v>
+      </c>
+      <c r="J888" s="1">
+        <v>409.08</v>
+      </c>
+      <c r="K888" s="1">
+        <v>460.39</v>
+      </c>
+      <c r="L888" s="1">
+        <v>464.19</v>
+      </c>
+      <c r="M888" s="1">
+        <v>432.52</v>
+      </c>
+      <c r="N888" s="1">
+        <v>491.67</v>
+      </c>
+      <c r="O888" s="1">
+        <v>475.82</v>
+      </c>
+      <c r="P888" s="1">
+        <v>562.93</v>
+      </c>
+      <c r="Q888" s="1">
+        <v>594.09</v>
+      </c>
+      <c r="R888" s="1">
+        <v>631.7</v>
+      </c>
+      <c r="S888" s="1">
+        <v>665.09</v>
+      </c>
+      <c r="T888" s="1">
+        <v>676.77</v>
+      </c>
+      <c r="U888" s="1">
+        <v>676.07</v>
+      </c>
+      <c r="V888" s="1">
+        <v>698.43</v>
+      </c>
+      <c r="W888" s="1">
+        <v>738.52</v>
+      </c>
+      <c r="X888" s="1">
+        <v>718.89</v>
+      </c>
+      <c r="Y888" s="1">
+        <v>643.06</v>
+      </c>
+      <c r="Z888" s="1">
+        <v>502.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31120" windowHeight="13700"/>
+    <workbookView windowHeight="13720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="909">
   <si>
     <t>日期</t>
   </si>
@@ -3721,7 +3721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z888"/>
+  <dimension ref="A1:Z892"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -74768,6 +74768,326 @@
         <v>502.8</v>
       </c>
     </row>
+    <row r="889" spans="1:26">
+      <c r="A889" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B889" t="s">
+        <v>27</v>
+      </c>
+      <c r="C889" s="1">
+        <v>538.01</v>
+      </c>
+      <c r="D889" s="1">
+        <v>495.75</v>
+      </c>
+      <c r="E889" s="1">
+        <v>480.02</v>
+      </c>
+      <c r="F889" s="1">
+        <v>441.02</v>
+      </c>
+      <c r="G889" s="1">
+        <v>412.03</v>
+      </c>
+      <c r="H889" s="1">
+        <v>403.3</v>
+      </c>
+      <c r="I889" s="1">
+        <v>405.67</v>
+      </c>
+      <c r="J889" s="1">
+        <v>390.87</v>
+      </c>
+      <c r="K889" s="1">
+        <v>397.17</v>
+      </c>
+      <c r="L889" s="1">
+        <v>405.89</v>
+      </c>
+      <c r="M889" s="1">
+        <v>394.7</v>
+      </c>
+      <c r="N889" s="1">
+        <v>443.83</v>
+      </c>
+      <c r="O889" s="1">
+        <v>410.51</v>
+      </c>
+      <c r="P889" s="1">
+        <v>529.66</v>
+      </c>
+      <c r="Q889" s="1">
+        <v>553.6</v>
+      </c>
+      <c r="R889" s="1">
+        <v>601.84</v>
+      </c>
+      <c r="S889" s="1">
+        <v>647.66</v>
+      </c>
+      <c r="T889" s="1">
+        <v>621.13</v>
+      </c>
+      <c r="U889" s="1">
+        <v>615.97</v>
+      </c>
+      <c r="V889" s="1">
+        <v>631</v>
+      </c>
+      <c r="W889" s="1">
+        <v>572.25</v>
+      </c>
+      <c r="X889" s="1">
+        <v>546.12</v>
+      </c>
+      <c r="Y889" s="1">
+        <v>511.4</v>
+      </c>
+      <c r="Z889" s="1">
+        <v>470.87</v>
+      </c>
+    </row>
+    <row r="890" spans="1:26">
+      <c r="A890" s="2">
+        <v>46180</v>
+      </c>
+      <c r="B890" t="s">
+        <v>27</v>
+      </c>
+      <c r="C890" s="1">
+        <v>556.08</v>
+      </c>
+      <c r="D890" s="1">
+        <v>515.13</v>
+      </c>
+      <c r="E890" s="1">
+        <v>418.88</v>
+      </c>
+      <c r="F890" s="1">
+        <v>405.37</v>
+      </c>
+      <c r="G890" s="1">
+        <v>395.21</v>
+      </c>
+      <c r="H890" s="1">
+        <v>391.94</v>
+      </c>
+      <c r="I890" s="1">
+        <v>391.41</v>
+      </c>
+      <c r="J890" s="1">
+        <v>376.54</v>
+      </c>
+      <c r="K890" s="1">
+        <v>367.38</v>
+      </c>
+      <c r="L890" s="1">
+        <v>367.36</v>
+      </c>
+      <c r="M890" s="1">
+        <v>373.23</v>
+      </c>
+      <c r="N890" s="1">
+        <v>423.28</v>
+      </c>
+      <c r="O890" s="1">
+        <v>434.11</v>
+      </c>
+      <c r="P890" s="1">
+        <v>487.66</v>
+      </c>
+      <c r="Q890" s="1">
+        <v>475.29</v>
+      </c>
+      <c r="R890" s="1">
+        <v>470.69</v>
+      </c>
+      <c r="S890" s="1">
+        <v>484.96</v>
+      </c>
+      <c r="T890" s="1">
+        <v>510.01</v>
+      </c>
+      <c r="U890" s="1">
+        <v>458.36</v>
+      </c>
+      <c r="V890" s="1">
+        <v>542.74</v>
+      </c>
+      <c r="W890" s="1">
+        <v>587.29</v>
+      </c>
+      <c r="X890" s="1">
+        <v>566.23</v>
+      </c>
+      <c r="Y890" s="1">
+        <v>504.17</v>
+      </c>
+      <c r="Z890" s="1">
+        <v>425.46</v>
+      </c>
+    </row>
+    <row r="891" spans="1:26">
+      <c r="A891" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B891" t="s">
+        <v>27</v>
+      </c>
+      <c r="C891" s="1">
+        <v>498.98</v>
+      </c>
+      <c r="D891" s="1">
+        <v>433.31</v>
+      </c>
+      <c r="E891" s="1">
+        <v>393.48</v>
+      </c>
+      <c r="F891" s="1">
+        <v>388.47</v>
+      </c>
+      <c r="G891" s="1">
+        <v>385.03</v>
+      </c>
+      <c r="H891" s="1">
+        <v>384</v>
+      </c>
+      <c r="I891" s="1">
+        <v>385.43</v>
+      </c>
+      <c r="J891" s="1">
+        <v>383.69</v>
+      </c>
+      <c r="K891" s="1">
+        <v>473.74</v>
+      </c>
+      <c r="L891" s="1">
+        <v>564.23</v>
+      </c>
+      <c r="M891" s="1">
+        <v>510.28</v>
+      </c>
+      <c r="N891" s="1">
+        <v>472.91</v>
+      </c>
+      <c r="O891" s="1">
+        <v>479.2</v>
+      </c>
+      <c r="P891" s="1">
+        <v>515.5</v>
+      </c>
+      <c r="Q891" s="1">
+        <v>521.23</v>
+      </c>
+      <c r="R891" s="1">
+        <v>543.17</v>
+      </c>
+      <c r="S891" s="1">
+        <v>633.44</v>
+      </c>
+      <c r="T891" s="1">
+        <v>591.9</v>
+      </c>
+      <c r="U891" s="1">
+        <v>513.86</v>
+      </c>
+      <c r="V891" s="1">
+        <v>596.73</v>
+      </c>
+      <c r="W891" s="1">
+        <v>565.19</v>
+      </c>
+      <c r="X891" s="1">
+        <v>490.17</v>
+      </c>
+      <c r="Y891" s="1">
+        <v>443.42</v>
+      </c>
+      <c r="Z891" s="1">
+        <v>414.25</v>
+      </c>
+    </row>
+    <row r="892" spans="1:26">
+      <c r="A892" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B892" t="s">
+        <v>27</v>
+      </c>
+      <c r="C892" s="1">
+        <v>502.72</v>
+      </c>
+      <c r="D892" s="1">
+        <v>417.33</v>
+      </c>
+      <c r="E892" s="1">
+        <v>408.6</v>
+      </c>
+      <c r="F892" s="1">
+        <v>409.65</v>
+      </c>
+      <c r="G892" s="1">
+        <v>383.21</v>
+      </c>
+      <c r="H892" s="1">
+        <v>379.92</v>
+      </c>
+      <c r="I892" s="1">
+        <v>386.57</v>
+      </c>
+      <c r="J892" s="1">
+        <v>377.51</v>
+      </c>
+      <c r="K892" s="1">
+        <v>444.64</v>
+      </c>
+      <c r="L892" s="1">
+        <v>501.38</v>
+      </c>
+      <c r="M892" s="1">
+        <v>452.51</v>
+      </c>
+      <c r="N892" s="1">
+        <v>506.77</v>
+      </c>
+      <c r="O892" s="1">
+        <v>476.79</v>
+      </c>
+      <c r="P892" s="1">
+        <v>565.85</v>
+      </c>
+      <c r="Q892" s="1">
+        <v>545.57</v>
+      </c>
+      <c r="R892" s="1">
+        <v>577.36</v>
+      </c>
+      <c r="S892" s="1">
+        <v>563.24</v>
+      </c>
+      <c r="T892" s="1">
+        <v>536.88</v>
+      </c>
+      <c r="U892" s="1">
+        <v>497.78</v>
+      </c>
+      <c r="V892" s="1">
+        <v>555.62</v>
+      </c>
+      <c r="W892" s="1">
+        <v>560.93</v>
+      </c>
+      <c r="X892" s="1">
+        <v>528.45</v>
+      </c>
+      <c r="Y892" s="1">
+        <v>465.35</v>
+      </c>
+      <c r="Z892" s="1">
+        <v>416.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="909">
   <si>
     <t>日期</t>
   </si>
@@ -3721,7 +3721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z892"/>
+  <dimension ref="A1:Z893"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -75088,6 +75088,86 @@
         <v>416.21</v>
       </c>
     </row>
+    <row r="893" spans="1:26">
+      <c r="A893" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B893" t="s">
+        <v>27</v>
+      </c>
+      <c r="C893" s="1">
+        <v>303.22</v>
+      </c>
+      <c r="D893" s="1">
+        <v>360.5</v>
+      </c>
+      <c r="E893" s="1">
+        <v>352.19</v>
+      </c>
+      <c r="F893" s="1">
+        <v>346.24</v>
+      </c>
+      <c r="G893" s="1">
+        <v>341.38</v>
+      </c>
+      <c r="H893" s="1">
+        <v>339.49</v>
+      </c>
+      <c r="I893" s="1">
+        <v>347.95</v>
+      </c>
+      <c r="J893" s="1">
+        <v>345.16</v>
+      </c>
+      <c r="K893" s="1">
+        <v>378.78</v>
+      </c>
+      <c r="L893" s="1">
+        <v>426.19</v>
+      </c>
+      <c r="M893" s="1">
+        <v>386.84</v>
+      </c>
+      <c r="N893" s="1">
+        <v>367.49</v>
+      </c>
+      <c r="O893" s="1">
+        <v>345.47</v>
+      </c>
+      <c r="P893" s="1">
+        <v>345.84</v>
+      </c>
+      <c r="Q893" s="1">
+        <v>406.16</v>
+      </c>
+      <c r="R893" s="1">
+        <v>419.48</v>
+      </c>
+      <c r="S893" s="1">
+        <v>496.71</v>
+      </c>
+      <c r="T893" s="1">
+        <v>485.89</v>
+      </c>
+      <c r="U893" s="1">
+        <v>431.48</v>
+      </c>
+      <c r="V893" s="1">
+        <v>550.57</v>
+      </c>
+      <c r="W893" s="1">
+        <v>466.38</v>
+      </c>
+      <c r="X893" s="1">
+        <v>423.69</v>
+      </c>
+      <c r="Y893" s="1">
+        <v>399.97</v>
+      </c>
+      <c r="Z893" s="1">
+        <v>379.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="909">
   <si>
     <t>日期</t>
   </si>
@@ -3721,7 +3721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z893"/>
+  <dimension ref="A1:Z894"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -75168,6 +75168,86 @@
         <v>379.48</v>
       </c>
     </row>
+    <row r="894" spans="1:26">
+      <c r="A894" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B894" t="s">
+        <v>27</v>
+      </c>
+      <c r="C894" s="1">
+        <v>378.34</v>
+      </c>
+      <c r="D894" s="1">
+        <v>365.33</v>
+      </c>
+      <c r="E894" s="1">
+        <v>356.14</v>
+      </c>
+      <c r="F894" s="1">
+        <v>351.46</v>
+      </c>
+      <c r="G894" s="1">
+        <v>351.38</v>
+      </c>
+      <c r="H894" s="1">
+        <v>350.37</v>
+      </c>
+      <c r="I894" s="1">
+        <v>352.51</v>
+      </c>
+      <c r="J894" s="1">
+        <v>350.82</v>
+      </c>
+      <c r="K894" s="1">
+        <v>393.6</v>
+      </c>
+      <c r="L894" s="1">
+        <v>440.3</v>
+      </c>
+      <c r="M894" s="1">
+        <v>383.3</v>
+      </c>
+      <c r="N894" s="1">
+        <v>368.93</v>
+      </c>
+      <c r="O894" s="1">
+        <v>372.15</v>
+      </c>
+      <c r="P894" s="1">
+        <v>440.63</v>
+      </c>
+      <c r="Q894" s="1">
+        <v>439.57</v>
+      </c>
+      <c r="R894" s="1">
+        <v>495.63</v>
+      </c>
+      <c r="S894" s="1">
+        <v>539.29</v>
+      </c>
+      <c r="T894" s="1">
+        <v>560.01</v>
+      </c>
+      <c r="U894" s="1">
+        <v>524.3</v>
+      </c>
+      <c r="V894" s="1">
+        <v>718.27</v>
+      </c>
+      <c r="W894" s="1">
+        <v>562.08</v>
+      </c>
+      <c r="X894" s="1">
+        <v>483.33</v>
+      </c>
+      <c r="Y894" s="1">
+        <v>406.12</v>
+      </c>
+      <c r="Z894" s="1">
+        <v>375.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="909">
   <si>
     <t>日期</t>
   </si>
@@ -3721,7 +3721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z894"/>
+  <dimension ref="A1:Z895"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -75248,6 +75248,86 @@
         <v>375.61</v>
       </c>
     </row>
+    <row r="895" spans="1:26">
+      <c r="A895" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B895" t="s">
+        <v>27</v>
+      </c>
+      <c r="C895" s="1">
+        <v>389.94</v>
+      </c>
+      <c r="D895" s="1">
+        <v>377</v>
+      </c>
+      <c r="E895" s="1">
+        <v>359.78</v>
+      </c>
+      <c r="F895" s="1">
+        <v>352.46</v>
+      </c>
+      <c r="G895" s="1">
+        <v>350.27</v>
+      </c>
+      <c r="H895" s="1">
+        <v>349.19</v>
+      </c>
+      <c r="I895" s="1">
+        <v>352.26</v>
+      </c>
+      <c r="J895" s="1">
+        <v>348.75</v>
+      </c>
+      <c r="K895" s="1">
+        <v>371.85</v>
+      </c>
+      <c r="L895" s="1">
+        <v>438.68</v>
+      </c>
+      <c r="M895" s="1">
+        <v>439.77</v>
+      </c>
+      <c r="N895" s="1">
+        <v>462.8</v>
+      </c>
+      <c r="O895" s="1">
+        <v>417.1</v>
+      </c>
+      <c r="P895" s="1">
+        <v>467.61</v>
+      </c>
+      <c r="Q895" s="1">
+        <v>437.9</v>
+      </c>
+      <c r="R895" s="1">
+        <v>451.89</v>
+      </c>
+      <c r="S895" s="1">
+        <v>528.14</v>
+      </c>
+      <c r="T895" s="1">
+        <v>540.01</v>
+      </c>
+      <c r="U895" s="1">
+        <v>502.62</v>
+      </c>
+      <c r="V895" s="1">
+        <v>653.15</v>
+      </c>
+      <c r="W895" s="1">
+        <v>565.13</v>
+      </c>
+      <c r="X895" s="1">
+        <v>502.03</v>
+      </c>
+      <c r="Y895" s="1">
+        <v>414.36</v>
+      </c>
+      <c r="Z895" s="1">
+        <v>386.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="909">
   <si>
     <t>日期</t>
   </si>
@@ -3721,7 +3721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z895"/>
+  <dimension ref="A1:Z896"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -75328,6 +75328,86 @@
         <v>386.17</v>
       </c>
     </row>
+    <row r="896" spans="1:26">
+      <c r="A896" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B896" t="s">
+        <v>27</v>
+      </c>
+      <c r="C896" s="1">
+        <v>438.3</v>
+      </c>
+      <c r="D896" s="1">
+        <v>409.32</v>
+      </c>
+      <c r="E896" s="1">
+        <v>383.52</v>
+      </c>
+      <c r="F896" s="1">
+        <v>361.57</v>
+      </c>
+      <c r="G896" s="1">
+        <v>358.03</v>
+      </c>
+      <c r="H896" s="1">
+        <v>352.15</v>
+      </c>
+      <c r="I896" s="1">
+        <v>351.67</v>
+      </c>
+      <c r="J896" s="1">
+        <v>344.83</v>
+      </c>
+      <c r="K896" s="1">
+        <v>388.56</v>
+      </c>
+      <c r="L896" s="1">
+        <v>403.34</v>
+      </c>
+      <c r="M896" s="1">
+        <v>384.26</v>
+      </c>
+      <c r="N896" s="1">
+        <v>437.3</v>
+      </c>
+      <c r="O896" s="1">
+        <v>393.04</v>
+      </c>
+      <c r="P896" s="1">
+        <v>418.9</v>
+      </c>
+      <c r="Q896" s="1">
+        <v>429.88</v>
+      </c>
+      <c r="R896" s="1">
+        <v>494.59</v>
+      </c>
+      <c r="S896" s="1">
+        <v>512.31</v>
+      </c>
+      <c r="T896" s="1">
+        <v>483.7</v>
+      </c>
+      <c r="U896" s="1">
+        <v>433.02</v>
+      </c>
+      <c r="V896" s="1">
+        <v>512.33</v>
+      </c>
+      <c r="W896" s="1">
+        <v>470.78</v>
+      </c>
+      <c r="X896" s="1">
+        <v>448.47</v>
+      </c>
+      <c r="Y896" s="1">
+        <v>428.18</v>
+      </c>
+      <c r="Z896" s="1">
+        <v>387.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32520" windowHeight="9700"/>
+    <workbookView windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -119,7 +119,7 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1101,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z906"/>
+  <dimension ref="A1:Z907"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
@@ -73587,6 +73587,86 @@
         <v>446.6</v>
       </c>
     </row>
+    <row r="907" spans="1:26">
+      <c r="A907" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B907" t="s">
+        <v>26</v>
+      </c>
+      <c r="C907">
+        <v>556.76</v>
+      </c>
+      <c r="D907">
+        <v>462.63</v>
+      </c>
+      <c r="E907">
+        <v>432.27</v>
+      </c>
+      <c r="F907">
+        <v>405.12</v>
+      </c>
+      <c r="G907">
+        <v>380.07</v>
+      </c>
+      <c r="H907">
+        <v>361.82</v>
+      </c>
+      <c r="I907">
+        <v>357.6</v>
+      </c>
+      <c r="J907">
+        <v>347.95</v>
+      </c>
+      <c r="K907">
+        <v>388.6</v>
+      </c>
+      <c r="L907">
+        <v>428.43</v>
+      </c>
+      <c r="M907">
+        <v>392.51</v>
+      </c>
+      <c r="N907">
+        <v>418.13</v>
+      </c>
+      <c r="O907">
+        <v>428.27</v>
+      </c>
+      <c r="P907">
+        <v>520.65</v>
+      </c>
+      <c r="Q907">
+        <v>497.62</v>
+      </c>
+      <c r="R907">
+        <v>519.75</v>
+      </c>
+      <c r="S907">
+        <v>585.08</v>
+      </c>
+      <c r="T907">
+        <v>550.89</v>
+      </c>
+      <c r="U907">
+        <v>560.26</v>
+      </c>
+      <c r="V907">
+        <v>691.86</v>
+      </c>
+      <c r="W907">
+        <v>600.78</v>
+      </c>
+      <c r="X907">
+        <v>622.09</v>
+      </c>
+      <c r="Y907">
+        <v>577.89</v>
+      </c>
+      <c r="Z907">
+        <v>440.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -1101,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z907"/>
+  <dimension ref="A1:Z908"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
@@ -73667,6 +73667,86 @@
         <v>440.85</v>
       </c>
     </row>
+    <row r="908" spans="1:26">
+      <c r="A908" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B908" t="s">
+        <v>26</v>
+      </c>
+      <c r="C908">
+        <v>779.44</v>
+      </c>
+      <c r="D908">
+        <v>598.65</v>
+      </c>
+      <c r="E908">
+        <v>476.29</v>
+      </c>
+      <c r="F908">
+        <v>424.54</v>
+      </c>
+      <c r="G908">
+        <v>391.77</v>
+      </c>
+      <c r="H908">
+        <v>371.2</v>
+      </c>
+      <c r="I908">
+        <v>367.19</v>
+      </c>
+      <c r="J908">
+        <v>342.94</v>
+      </c>
+      <c r="K908">
+        <v>407.83</v>
+      </c>
+      <c r="L908">
+        <v>480.54</v>
+      </c>
+      <c r="M908">
+        <v>455.09</v>
+      </c>
+      <c r="N908">
+        <v>485.27</v>
+      </c>
+      <c r="O908">
+        <v>493.98</v>
+      </c>
+      <c r="P908">
+        <v>607.76</v>
+      </c>
+      <c r="Q908">
+        <v>599.19</v>
+      </c>
+      <c r="R908">
+        <v>578.35</v>
+      </c>
+      <c r="S908">
+        <v>656.23</v>
+      </c>
+      <c r="T908">
+        <v>583.69</v>
+      </c>
+      <c r="U908">
+        <v>515.57</v>
+      </c>
+      <c r="V908">
+        <v>626.62</v>
+      </c>
+      <c r="W908">
+        <v>645.43</v>
+      </c>
+      <c r="X908">
+        <v>648.6</v>
+      </c>
+      <c r="Y908">
+        <v>687.23</v>
+      </c>
+      <c r="Z908">
+        <v>484.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -1101,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z908"/>
+  <dimension ref="A1:Z909"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
@@ -73747,6 +73747,86 @@
         <v>484.22</v>
       </c>
     </row>
+    <row r="909" spans="1:26">
+      <c r="A909" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B909" t="s">
+        <v>26</v>
+      </c>
+      <c r="C909">
+        <v>689.97</v>
+      </c>
+      <c r="D909">
+        <v>588.67</v>
+      </c>
+      <c r="E909">
+        <v>492.5</v>
+      </c>
+      <c r="F909">
+        <v>477.47</v>
+      </c>
+      <c r="G909">
+        <v>430.39</v>
+      </c>
+      <c r="H909">
+        <v>410.62</v>
+      </c>
+      <c r="I909">
+        <v>415.31</v>
+      </c>
+      <c r="J909">
+        <v>406.45</v>
+      </c>
+      <c r="K909">
+        <v>489.04</v>
+      </c>
+      <c r="L909">
+        <v>586.84</v>
+      </c>
+      <c r="M909">
+        <v>539</v>
+      </c>
+      <c r="N909">
+        <v>561.39</v>
+      </c>
+      <c r="O909">
+        <v>478.19</v>
+      </c>
+      <c r="P909">
+        <v>605.03</v>
+      </c>
+      <c r="Q909">
+        <v>556.18</v>
+      </c>
+      <c r="R909">
+        <v>509.02</v>
+      </c>
+      <c r="S909">
+        <v>601.64</v>
+      </c>
+      <c r="T909">
+        <v>603.78</v>
+      </c>
+      <c r="U909">
+        <v>523.9</v>
+      </c>
+      <c r="V909">
+        <v>687.25</v>
+      </c>
+      <c r="W909">
+        <v>588.53</v>
+      </c>
+      <c r="X909">
+        <v>575.57</v>
+      </c>
+      <c r="Y909">
+        <v>547.22</v>
+      </c>
+      <c r="Z909">
+        <v>447.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="13580"/>
+    <workbookView windowWidth="29920" windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -1101,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z909"/>
+  <dimension ref="A1:Z910"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
@@ -73827,6 +73827,86 @@
         <v>447.92</v>
       </c>
     </row>
+    <row r="910" spans="1:26">
+      <c r="A910" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B910" t="s">
+        <v>26</v>
+      </c>
+      <c r="C910">
+        <v>743.34</v>
+      </c>
+      <c r="D910">
+        <v>708.33</v>
+      </c>
+      <c r="E910">
+        <v>481.08</v>
+      </c>
+      <c r="F910">
+        <v>407.61</v>
+      </c>
+      <c r="G910">
+        <v>372.73</v>
+      </c>
+      <c r="H910">
+        <v>359.73</v>
+      </c>
+      <c r="I910">
+        <v>360.79</v>
+      </c>
+      <c r="J910">
+        <v>357.91</v>
+      </c>
+      <c r="K910">
+        <v>417.73</v>
+      </c>
+      <c r="L910">
+        <v>498.14</v>
+      </c>
+      <c r="M910">
+        <v>509.87</v>
+      </c>
+      <c r="N910">
+        <v>576.86</v>
+      </c>
+      <c r="O910">
+        <v>513.74</v>
+      </c>
+      <c r="P910">
+        <v>622.47</v>
+      </c>
+      <c r="Q910">
+        <v>618</v>
+      </c>
+      <c r="R910">
+        <v>599.99</v>
+      </c>
+      <c r="S910">
+        <v>654.33</v>
+      </c>
+      <c r="T910">
+        <v>608.16</v>
+      </c>
+      <c r="U910">
+        <v>566.45</v>
+      </c>
+      <c r="V910">
+        <v>722.43</v>
+      </c>
+      <c r="W910">
+        <v>642.15</v>
+      </c>
+      <c r="X910">
+        <v>624.12</v>
+      </c>
+      <c r="Y910">
+        <v>593.87</v>
+      </c>
+      <c r="Z910">
+        <v>518.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -1101,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z910"/>
+  <dimension ref="A1:Z911"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
@@ -73907,6 +73907,86 @@
         <v>518.42</v>
       </c>
     </row>
+    <row r="911" spans="1:26">
+      <c r="A911" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B911" t="s">
+        <v>26</v>
+      </c>
+      <c r="C911">
+        <v>448.49</v>
+      </c>
+      <c r="D911">
+        <v>438.05</v>
+      </c>
+      <c r="E911">
+        <v>401.57</v>
+      </c>
+      <c r="F911">
+        <v>385.13</v>
+      </c>
+      <c r="G911">
+        <v>356.94</v>
+      </c>
+      <c r="H911">
+        <v>350.92</v>
+      </c>
+      <c r="I911">
+        <v>358.46</v>
+      </c>
+      <c r="J911">
+        <v>338.66</v>
+      </c>
+      <c r="K911">
+        <v>337.11</v>
+      </c>
+      <c r="L911">
+        <v>369.94</v>
+      </c>
+      <c r="M911">
+        <v>355.05</v>
+      </c>
+      <c r="N911">
+        <v>355.92</v>
+      </c>
+      <c r="O911">
+        <v>406.34</v>
+      </c>
+      <c r="P911">
+        <v>416.94</v>
+      </c>
+      <c r="Q911">
+        <v>366.28</v>
+      </c>
+      <c r="R911">
+        <v>374.82</v>
+      </c>
+      <c r="S911">
+        <v>392.94</v>
+      </c>
+      <c r="T911">
+        <v>418.86</v>
+      </c>
+      <c r="U911">
+        <v>392.95</v>
+      </c>
+      <c r="V911">
+        <v>408.49</v>
+      </c>
+      <c r="W911">
+        <v>407.61</v>
+      </c>
+      <c r="X911">
+        <v>409.28</v>
+      </c>
+      <c r="Y911">
+        <v>399.14</v>
+      </c>
+      <c r="Z911">
+        <v>377.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/日前节点电价.xlsx
+++ b/日前节点电价.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29920" windowHeight="13580"/>
+    <workbookView windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -1101,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z911"/>
+  <dimension ref="A1:Z912"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
@@ -73987,6 +73987,86 @@
         <v>377.92</v>
       </c>
     </row>
+    <row r="912" spans="1:26">
+      <c r="A912" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B912" t="s">
+        <v>26</v>
+      </c>
+      <c r="C912">
+        <v>378.66</v>
+      </c>
+      <c r="D912">
+        <v>365.11</v>
+      </c>
+      <c r="E912">
+        <v>358.49</v>
+      </c>
+      <c r="F912">
+        <v>340.36</v>
+      </c>
+      <c r="G912">
+        <v>326.73</v>
+      </c>
+      <c r="H912">
+        <v>321.31</v>
+      </c>
+      <c r="I912">
+        <v>327.68</v>
+      </c>
+      <c r="J912">
+        <v>324.59</v>
+      </c>
+      <c r="K912">
+        <v>355.64</v>
+      </c>
+      <c r="L912">
+        <v>414.04</v>
+      </c>
+      <c r="M912">
+        <v>438.21</v>
+      </c>
+      <c r="N912">
+        <v>478.49</v>
+      </c>
+      <c r="O912">
+        <v>487.27</v>
+      </c>
+      <c r="P912">
+        <v>480.59</v>
+      </c>
+      <c r="Q912">
+        <v>392.17</v>
+      </c>
+      <c r="R912">
+        <v>375.24</v>
+      </c>
+      <c r="S912">
+        <v>393.26</v>
+      </c>
+      <c r="T912">
+        <v>414.38</v>
+      </c>
+      <c r="U912">
+        <v>398.75</v>
+      </c>
+      <c r="V912">
+        <v>501.9</v>
+      </c>
+      <c r="W912">
+        <v>488.5</v>
+      </c>
+      <c r="X912">
+        <v>469.68</v>
+      </c>
+      <c r="Y912">
+        <v>390.73</v>
+      </c>
+      <c r="Z912">
+        <v>367.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
